--- a/Lab_4/data/partB/param_optimization_process/v100_k20_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k20_s150_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -573,16 +573,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -591,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,46 +677,46 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -729,25 +729,25 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -756,19 +756,19 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
         <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -790,10 +790,10 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -802,13 +802,13 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>6</v>
@@ -820,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,37 +842,37 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
         <v>7</v>
       </c>
-      <c r="G8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9</v>
-      </c>
       <c r="I8" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -894,34 +894,34 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>5</v>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
         <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,46 +1090,46 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1151,40 +1151,40 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1206,19 +1206,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1227,13 +1227,13 @@
         <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1249,19 +1249,19 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1270,25 +1270,25 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
         <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18539,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19372,7 +19372,7 @@
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22585,7 +22585,7 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22806,7 +22806,7 @@
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23061,7 @@
       </c>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
